--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104620_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104620_W18.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2036</v>
+        <v>4.5406</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4873</v>
+        <v>2.1443</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2836</v>
+        <v>2.3963</v>
       </c>
       <c r="G2" t="n">
-        <v>1.292</v>
+        <v>2.5972</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0116</v>
+        <v>0.996</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7196</v>
+        <v>1.6012</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7694</v>
+        <v>2.1491</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5082</v>
+        <v>0.6378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2612</v>
+        <v>1.5114</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4774</v>
+        <v>0.4481</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4966</v>
+        <v>0.3583</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9808</v>
+        <v>0.0898</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.8147</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0627</v>
+        <v>1.0709</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6816</v>
+        <v>0.4991</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3811</v>
+        <v>0.5718</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6636</v>
+        <v>1.7831</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5314</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8678</v>
+        <v>0.6936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0508</v>
+        <v>4.0861</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6864</v>
+        <v>6.3331</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3644</v>
+        <v>-2.247</v>
       </c>
       <c r="G3" t="n">
-        <v>2.59</v>
+        <v>1.2949</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854000000000001</v>
+        <v>2.0051</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6046</v>
+        <v>-0.7101</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1653</v>
+        <v>3.7458</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6407</v>
+        <v>3.4851</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5246</v>
+        <v>0.2607</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4247</v>
+        <v>-2.4508</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3446</v>
+        <v>-1.48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08</v>
+        <v>-0.9708</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5878</v>
+        <v>0.9568</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0162</v>
+        <v>0.5757</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5716</v>
+        <v>0.3812</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7803</v>
+        <v>3.6554</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>4.5157</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6876</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0957</v>
+        <v>3.697</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6518</v>
+        <v>3.3432</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4438</v>
+        <v>0.3538</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4445</v>
+        <v>3.4489</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.042</v>
+        <v>-0.0321</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4865</v>
+        <v>3.481</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5065</v>
+        <v>4.4783</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8382</v>
+        <v>3.8201</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.062</v>
+        <v>-1.0295</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4525</v>
+        <v>0.1511</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9739</v>
+        <v>-0.2442</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5214</v>
+        <v>0.3953</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7842</v>
+        <v>0.7799</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3365</v>
+        <v>1.4868</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2816</v>
+        <v>1.4471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0549</v>
+        <v>0.0398</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2501</v>
+        <v>1.2404</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9772</v>
+        <v>1.9559</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8977</v>
+        <v>1.8837</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0735</v>
+        <v>-1.0603</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.206</v>
+        <v>0.3635</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4688</v>
+        <v>-0.2812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6747</v>
+        <v>0.6448</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.53</v>
+        <v>0.5178</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6502</v>
+        <v>1.2525</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1802</v>
+        <v>-0.7346</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1037</v>
+        <v>2.0908</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1054</v>
+        <v>-1.0976</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2091</v>
+        <v>3.1883</v>
       </c>
       <c r="J6" t="n">
-        <v>3.323</v>
+        <v>3.2782</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L6" t="n">
-        <v>3.7181</v>
+        <v>3.6853</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2193</v>
+        <v>-1.1874</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8961</v>
+        <v>0.1707</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0434</v>
+        <v>-0.3836</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1473</v>
+        <v>0.5543</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5664</v>
+        <v>-0.3406</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.336</v>
+        <v>-1.0427</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7696</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1625</v>
+        <v>-1.1435</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2455</v>
+        <v>-0.2306</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9169</v>
+        <v>-0.913</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4386</v>
+        <v>-0.4428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5251</v>
+        <v>-0.529</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7239</v>
+        <v>-0.7007</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2562</v>
+        <v>-0.0452</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7652</v>
+        <v>-0.4601</v>
       </c>
       <c r="U7" t="n">
-        <v>0.509</v>
+        <v>0.4149</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3986</v>
+        <v>0.3929</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.7054</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2385</v>
+        <v>-0.0514</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6621</v>
+        <v>-0.654</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1703</v>
+        <v>-0.1668</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.7268</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1093</v>
+        <v>0.1089</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0099</v>
+        <v>-1.0025</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0.1881</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>-0.1604</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3478</v>
+        <v>0.3485</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2547</v>
+        <v>-1.2969</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1041</v>
+        <v>-2.0251</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1506</v>
+        <v>0.7282</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5282</v>
+        <v>2.1228</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7619</v>
+        <v>1.5103</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2337</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8648</v>
+        <v>1.9196</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4861</v>
+        <v>1.1376</v>
       </c>
       <c r="L9" t="n">
-        <v>2.351</v>
+        <v>0.782</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.393</v>
+        <v>0.2032</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2758</v>
+        <v>0.3727</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1172</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.046</v>
+        <v>0.028</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6079</v>
+        <v>-0.4392</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5619</v>
+        <v>0.4672</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.3991</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4972</v>
+        <v>-1.4351</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2623</v>
+        <v>-1.0521</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7651</v>
+        <v>-0.383</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1112</v>
+        <v>-0.5245</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5034</v>
+        <v>-2.7574</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6078</v>
+        <v>2.2329</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9266</v>
+        <v>0.8528</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1429</v>
+        <v>-1.4931</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7837</v>
+        <v>2.3459</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1847</v>
+        <v>-1.3774</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3605</v>
+        <v>-1.2643</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0415</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1657</v>
+        <v>-0.2276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>-0.5391</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5299</v>
+        <v>0.3115</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4012</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2821</v>
+        <v>-4.1463</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6717</v>
+        <v>-3.5208</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6104</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5166</v>
+        <v>-2.0932</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4908</v>
+        <v>0.8073</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0258</v>
+        <v>-2.9005</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4196</v>
+        <v>-0.875</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1559</v>
+        <v>1.3822</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5754</v>
+        <v>-2.2572</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0971</v>
+        <v>-1.2182</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.5749</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4504</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3953</v>
+        <v>0.1533</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1089</v>
+        <v>-0.1418</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2864</v>
+        <v>0.2951</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4515</v>
+        <v>-4.1505</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7459</v>
+        <v>-2.6655</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7056</v>
+        <v>-1.485</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0823</v>
+        <v>-2.5049</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8125</v>
+        <v>-0.4775</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8948</v>
+        <v>-2.0274</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8516</v>
+        <v>-1.4318</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3956</v>
+        <v>0.1551</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2471</v>
+        <v>-1.587</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2308</v>
+        <v>-1.0731</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5831</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.4405</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1669</v>
+        <v>0.5122</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3992</v>
+        <v>0.1321</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2323</v>
+        <v>0.3801</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.204000000000002</v>
+        <v>2.253499999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>3.398800000000002</v>
+        <v>4.162600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1947</v>
+        <v>-1.9089</v>
       </c>
       <c r="G13" t="n">
-        <v>5.254799999999999</v>
+        <v>5.2906</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1506999999999997</v>
+        <v>0.2119999999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>5.104399999999998</v>
+        <v>5.078399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>15.9323</v>
+        <v>15.739</v>
       </c>
       <c r="K13" t="n">
-        <v>5.830900000000001</v>
+        <v>5.7487</v>
       </c>
       <c r="L13" t="n">
-        <v>10.1015</v>
+        <v>9.990400000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.6775</v>
+        <v>-10.4486</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.6806</v>
+        <v>-5.5365</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.9972</v>
+        <v>-4.9119</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0125</v>
+        <v>-17.0723</v>
       </c>
       <c r="R13" t="n">
-        <v>6.805</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2684</v>
+        <v>3.321800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4951</v>
+        <v>-1.4427</v>
       </c>
       <c r="U13" t="n">
-        <v>4.763400000000001</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>3.8885</v>
+        <v>3.884600000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.974099999999998</v>
+        <v>6.9388</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0855</v>
+        <v>-3.0541</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0339</v>
+        <v>2.496</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6441</v>
+        <v>3.273</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6102</v>
+        <v>-0.777</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6272</v>
+        <v>2.6286</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4806</v>
+        <v>2.4733</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1467</v>
+        <v>0.1553</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2716</v>
+        <v>3.2571</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0477</v>
+        <v>3.0337</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6444</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1118</v>
+        <v>0.5715</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4386</v>
+        <v>0.0858</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6732</v>
+        <v>0.4857</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2415</v>
+        <v>1.9586</v>
       </c>
       <c r="E15" t="n">
-        <v>1.359</v>
+        <v>1.7468</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8825</v>
+        <v>0.2119</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8905</v>
+        <v>1.1282</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3574</v>
+        <v>2.5855</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.533</v>
+        <v>-1.4573</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0893</v>
+        <v>2.9737</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1048</v>
+        <v>3.3472</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1941</v>
+        <v>-0.3735</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9798</v>
+        <v>-1.8455</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2526</v>
+        <v>-0.7617</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7272</v>
+        <v>-1.0838</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2473</v>
+        <v>-0.3973</v>
       </c>
       <c r="T15" t="n">
-        <v>1.107</v>
+        <v>-1.1084</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1403</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6105</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6105</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6268</v>
+        <v>1.159</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4519</v>
+        <v>-0.0982</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1749</v>
+        <v>1.2572</v>
       </c>
       <c r="G16" t="n">
-        <v>1.15</v>
+        <v>-0.9074</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5975</v>
+        <v>-0.3834</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4475</v>
+        <v>-0.5239</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0203</v>
+        <v>1.0527</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3697</v>
+        <v>-0.1389</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3494</v>
+        <v>1.1916</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8702</v>
+        <v>-1.9601</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7721</v>
+        <v>-0.2446</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0981</v>
+        <v>-1.7155</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7501</v>
+        <v>0.1786</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4608</v>
+        <v>-0.3071</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7107</v>
+        <v>0.4857</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>-0.6162</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>-0.6162</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2107</v>
+        <v>1.0281</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9789</v>
+        <v>1.4521</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7682</v>
+        <v>-0.424</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7337</v>
+        <v>0.9062</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2539</v>
+        <v>0.1062</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4798</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0636</v>
+        <v>1.5218</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5066</v>
+        <v>0.293</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.2288</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3299</v>
+        <v>-0.6157</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2526</v>
+        <v>-0.1868</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0772</v>
+        <v>-0.4289</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8892</v>
+        <v>-0.1057</v>
       </c>
       <c r="T17" t="n">
-        <v>0.369</v>
+        <v>-0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5202</v>
+        <v>-0.0359</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9954</v>
+        <v>1.0258</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4563</v>
+        <v>1.6113</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4609</v>
+        <v>-0.5855</v>
       </c>
       <c r="G18" t="n">
-        <v>0.905</v>
+        <v>1.7378</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1053</v>
+        <v>1.255</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7997</v>
+        <v>0.4828</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5258</v>
+        <v>2.0505</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2944</v>
+        <v>1.4996</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2315</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6209</v>
+        <v>-0.3127</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1891</v>
+        <v>-0.2446</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1364</v>
+        <v>0.6946</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>0.0161</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0668</v>
+        <v>0.6785</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7864</v>
+        <v>-0.4009</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7864</v>
+        <v>0.7695</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.1704</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7864</v>
+        <v>-0.2279</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.8623</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7864</v>
+        <v>-1.0902</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7864</v>
+        <v>1.3178</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.4372</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7864</v>
+        <v>-0.1194</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.5457</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.5749</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.9708</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.272</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1884</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8452</v>
+        <v>-0.6178</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4487</v>
+        <v>-1.2943</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2939</v>
+        <v>0.6765</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2209</v>
+        <v>-2.3379</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8746</v>
+        <v>-1.5765</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0955</v>
+        <v>-0.7614</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3431</v>
+        <v>-0.1489</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4577</v>
+        <v>-1.3175</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1147</v>
+        <v>1.1686</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5639</v>
+        <v>-2.189</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5831</v>
+        <v>-0.259</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9808</v>
+        <v>-1.93</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5317</v>
+        <v>0.1754</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6261</v>
+        <v>-0.6415</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0944</v>
+        <v>0.8168</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0479</v>
+        <v>-0.7896</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7249</v>
+        <v>-0.7896</v>
       </c>
       <c r="F21" t="n">
-        <v>0.677</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3283</v>
+        <v>-0.7896</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5713</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.757</v>
+        <v>-0.7896</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1167</v>
+        <v>-0.7896</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3028</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.186</v>
+        <v>-0.7896</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2116</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2685</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9431</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2659</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8471</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4588</v>
+        <v>-0.8023</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1018</v>
+        <v>-0.516</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.357</v>
+        <v>-0.2862</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5249</v>
+        <v>-0.9936</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3463</v>
+        <v>-2.5935</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1786</v>
+        <v>1.5999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0373</v>
+        <v>1.2952</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-1.8173</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>3.1126</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5622</v>
+        <v>-2.2888</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3463</v>
+        <v>-0.7761</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2159</v>
+        <v>-1.5127</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>2.2763</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>2.7316</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4537</v>
+        <v>-0.6086</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>-0.969</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3145</v>
+        <v>0.3605</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7071</v>
+        <v>-1.4764</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.509</v>
+        <v>-1.2726</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8367</v>
+        <v>-1.4607</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6723</v>
+        <v>0.1881</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9937</v>
+        <v>-1.3514</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.593</v>
+        <v>-0.2702</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5993</v>
+        <v>-1.0812</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3243</v>
+        <v>-0.0202</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8049</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>3.1292</v>
+        <v>-0.6407</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3179</v>
+        <v>-1.3312</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.788</v>
+        <v>-0.8907</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5299</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3053</v>
+        <v>-0.5342</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3217</v>
+        <v>-0.4601</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0163</v>
+        <v>-0.0741</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4783</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5476</v>
+        <v>-1.4521</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6827</v>
+        <v>-0.1022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1351</v>
+        <v>-1.3499</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3617</v>
+        <v>-0.5219</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2742</v>
+        <v>-0.3447</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0875</v>
+        <v>-0.1772</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0137</v>
+        <v>0.0372</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6234</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6371</v>
+        <v>0.0372</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.348</v>
+        <v>-0.5592</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8976</v>
+        <v>-0.3447</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4504</v>
+        <v>-0.2144</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8003</v>
+        <v>-0.4553</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6956</v>
+        <v>-0.1394</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1047</v>
+        <v>-0.3159</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>-0.7025</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1177</v>
+        <v>-2.7507</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0117</v>
+        <v>-2.6826</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.106</v>
+        <v>-0.068</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5645</v>
+        <v>-4.5616</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.3202</v>
+        <v>-2.3261</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.2443</v>
+        <v>-2.2355</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0811</v>
+        <v>-2.0988</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4067</v>
+        <v>-1.4209</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4834</v>
+        <v>-2.4628</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2733</v>
+        <v>-0.9222</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2521</v>
+        <v>-0.8993</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0212</v>
+        <v>-0.0229</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.0965</v>
+        <v>-0.0863</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2043</v>
+        <v>-0.418499999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.194699999999999</v>
+        <v>1.9091</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.399</v>
+        <v>-2.327300000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.255</v>
+        <v>-5.2905</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1505000000000005</v>
+        <v>-0.2121</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.1043</v>
+        <v>-5.0784</v>
       </c>
       <c r="J26" t="n">
-        <v>10.6774</v>
+        <v>10.4485</v>
       </c>
       <c r="K26" t="n">
-        <v>5.6803</v>
+        <v>5.5366</v>
       </c>
       <c r="L26" t="n">
-        <v>4.997</v>
+        <v>4.912000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-15.9322</v>
+        <v>-15.7392</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.8306</v>
+        <v>-5.7487</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.1015</v>
+        <v>-9.990399999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>10.2075</v>
+        <v>10.2433</v>
       </c>
       <c r="Q26" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.2684</v>
+        <v>-1.4868</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.763400000000001</v>
+        <v>-4.764600000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>2.495000000000001</v>
+        <v>3.278</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.8886</v>
+        <v>-3.8845</v>
       </c>
       <c r="W26" t="n">
-        <v>3.0855</v>
+        <v>3.0541</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.974099999999999</v>
+        <v>-6.938699999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104620_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104620_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6936</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.6251</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.0541</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.0863</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104620_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.938699999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
